--- a/output/figures/state_superintendent_coverage_2014.xlsx
+++ b/output/figures/state_superintendent_coverage_2014.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -441,343 +441,400 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ga</t>
+          <t>fl</t>
         </is>
       </c>
       <c r="B5">
-        <v>1717805</v>
+        <v>2745223</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="D5">
-        <v>180</v>
+        <v>70</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>77.09999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ia</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="B6">
-        <v>505311</v>
+        <v>1717805</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
       <c r="D6">
-        <v>346</v>
+        <v>180</v>
       </c>
       <c r="E6">
-        <v>97.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>il</t>
+          <t>ia</t>
         </is>
       </c>
       <c r="B7">
-        <v>2046476</v>
+        <v>505311</v>
       </c>
       <c r="C7">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>862</v>
+        <v>346</v>
       </c>
       <c r="E7">
-        <v>98.3</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>il</t>
         </is>
       </c>
       <c r="B8">
-        <v>1004622</v>
+        <v>2046476</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D8">
-        <v>291</v>
+        <v>862</v>
       </c>
       <c r="E8">
-        <v>99.7</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ks</t>
+          <t>in</t>
         </is>
       </c>
       <c r="B9">
-        <v>496920</v>
+        <v>1004622</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="E9">
-        <v>93.2</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mi</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="B10">
-        <v>1350667</v>
+        <v>496920</v>
       </c>
       <c r="C10">
         <v>100</v>
       </c>
       <c r="D10">
-        <v>543</v>
+        <v>307</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mo</t>
+          <t>mi</t>
         </is>
       </c>
       <c r="B11">
-        <v>897427</v>
+        <v>1350667</v>
       </c>
       <c r="C11">
-        <v>93.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D11">
-        <v>520</v>
+        <v>543</v>
       </c>
       <c r="E11">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ne</t>
+          <t>mo</t>
         </is>
       </c>
       <c r="B12">
-        <v>312281</v>
+        <v>897427</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D12">
-        <v>251</v>
+        <v>520</v>
       </c>
       <c r="E12">
-        <v>97.59999999999999</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nj</t>
+          <t>nc</t>
         </is>
       </c>
       <c r="B13">
-        <v>1363220</v>
+        <v>1465031</v>
       </c>
       <c r="C13">
         <v>100</v>
       </c>
       <c r="D13">
-        <v>588</v>
+        <v>115</v>
       </c>
       <c r="E13">
-        <v>99.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ny</t>
+          <t>ne</t>
         </is>
       </c>
       <c r="B14">
-        <v>1637426</v>
+        <v>312281</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14">
-        <v>688</v>
+        <v>251</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>oh</t>
+          <t>nj</t>
         </is>
       </c>
       <c r="B15">
-        <v>1601836</v>
+        <v>1363220</v>
       </c>
       <c r="C15">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D15">
-        <v>615</v>
+        <v>588</v>
       </c>
       <c r="E15">
-        <v>99</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>ny</t>
         </is>
       </c>
       <c r="B16">
-        <v>671715</v>
+        <v>1637426</v>
       </c>
       <c r="C16">
         <v>100</v>
       </c>
       <c r="D16">
-        <v>517</v>
+        <v>688</v>
       </c>
       <c r="E16">
-        <v>99.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>or</t>
+          <t>oh</t>
         </is>
       </c>
       <c r="B17">
-        <v>566951</v>
+        <v>1601836</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D17">
-        <v>181</v>
+        <v>615</v>
       </c>
       <c r="E17">
-        <v>98.90000000000001</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pa</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="B18">
-        <v>1589440</v>
+        <v>671715</v>
       </c>
       <c r="C18">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="E18">
-        <v>99.40000000000001</v>
+        <v>99.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tx</t>
+          <t>or</t>
         </is>
       </c>
       <c r="B19">
-        <v>5003912</v>
+        <v>566951</v>
       </c>
       <c r="C19">
-        <v>80.3</v>
+        <v>100</v>
       </c>
       <c r="D19">
-        <v>1026</v>
+        <v>181</v>
       </c>
       <c r="E19">
-        <v>77.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>va</t>
+          <t>pa</t>
         </is>
       </c>
       <c r="B20">
-        <v>1265944</v>
+        <v>1589440</v>
       </c>
       <c r="C20">
-        <v>98.40000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D20">
-        <v>130</v>
+        <v>501</v>
       </c>
       <c r="E20">
-        <v>97.7</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>wi</t>
+          <t>tn</t>
         </is>
       </c>
       <c r="B21">
-        <v>860784</v>
+        <v>995475</v>
       </c>
       <c r="C21">
-        <v>99.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="D21">
-        <v>422</v>
+        <v>146</v>
       </c>
       <c r="E21">
-        <v>98.59999999999999</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>tx</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>5003912</v>
+      </c>
+      <c r="C22">
+        <v>99.2</v>
+      </c>
+      <c r="D22">
+        <v>1026</v>
+      </c>
+      <c r="E22">
+        <v>98.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>va</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1265944</v>
+      </c>
+      <c r="C23">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="D23">
+        <v>130</v>
+      </c>
+      <c r="E23">
+        <v>97.7</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>wi</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>860784</v>
+      </c>
+      <c r="C24">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="D24">
+        <v>422</v>
+      </c>
+      <c r="E24">
+        <v>98.59999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B25">
         <v>47489409</v>
       </c>
-      <c r="C22">
-        <v>61</v>
-      </c>
-      <c r="D22">
+      <c r="C25">
+        <v>71.8</v>
+      </c>
+      <c r="D25">
         <v>13080</v>
       </c>
-      <c r="E22">
-        <v>68.8</v>
+      <c r="E25">
+        <v>72.8</v>
       </c>
     </row>
   </sheetData>
